--- a/public/templates/kp-template-11.xlsx
+++ b/public/templates/kp-template-11.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mp-calc-2.0\price-calc\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A8D6466-447C-483D-9527-4344006DE3D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A1F3D46-8650-4BED-B1E1-FDFD5486289B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="КП-1 (с НДС) RUS" sheetId="16" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Лого" sheetId="17" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'КП-1 (с НДС) RUS'!$A$1:$F$55</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'КП-1 (с НДС) RUS'!$A$1:$F$54</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'КП-2 (со СКИДКОЙ) RUS'!$A$1:$I$54</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="27">
   <si>
     <t>№</t>
   </si>
@@ -127,158 +127,6 @@
     <t>Страна производитель:</t>
   </si>
   <si>
-    <t>Отметить значком       страны из которых поставляют товары указанные в данном Коммерческое предложение</t>
-  </si>
-  <si>
-    <t>Отметить значком       , те системы или группы товаров, по которым предоставляется данное Коммерческое предложение</t>
-  </si>
-  <si>
-    <t>Указать дату от которого выставляется данное Коммерческое предложение</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Менеджер сам в праве что указать в "шапке" таблицы:
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Цена</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> или  - </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Цена с НДС</t>
-    </r>
-  </si>
-  <si>
-    <t>Поле в котором указывается какая-то необходимая, общая информация по объекту</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Отметить значком       выгоды предоставляемые клиенту.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Проставлять только после общения с клиентом</t>
-    </r>
-  </si>
-  <si>
-    <t>Поле в котором указываются Приложения к донному Коммерческому приложению: Узлы, фотографии, Характеристики товара, Рекомендации и т.п.</t>
-  </si>
-  <si>
-    <t>Указать номер бланка коммерческого предложения</t>
-  </si>
-  <si>
-    <t>Указать свою должность
-Фамилию имя отчество
-Контактные данные</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Прописат срок действия Коммерческого предложения, но не более </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> дней</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">- Наименование товаров указывается так же как и в 1С
-- Единици езмерения указываются </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"УДОБНО"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-- Кол-во товаров указывается кратно таре (упаковки, пачки, коробки, ведра, руллоны и т.п.)
-- Цена устанавливается не менее минимальной цены
-</t>
-    </r>
-  </si>
-  <si>
-    <t>Правила заполнения КП</t>
-  </si>
-  <si>
-    <t>Что нельзя делать с КП</t>
-  </si>
-  <si>
-    <t>1. нельзя изменять шрифр (тип, размер, формат)</t>
-  </si>
-  <si>
-    <t>2. Название товаров в табличную часть заноситься только в формате "Calibri" размером 11</t>
-  </si>
-  <si>
     <t>НДС</t>
   </si>
   <si>
@@ -306,52 +154,12 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _₽_-;\-* #,##0.00\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -458,14 +266,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="0"/>
       <name val="Calibri"/>
@@ -477,29 +277,6 @@
       <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="20"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -531,7 +308,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -794,30 +571,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
@@ -876,20 +629,22 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -897,228 +652,189 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="25" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1153,8 +869,8 @@
       <xdr:rowOff>40748</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1404360</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>4185</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>79374</xdr:rowOff>
     </xdr:to>
@@ -1171,8 +887,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3277321" y="40748"/>
-          <a:ext cx="4466456" cy="1515002"/>
+          <a:off x="3264621" y="40748"/>
+          <a:ext cx="4188114" cy="1553101"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1312,13 +1028,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>74083</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1392,13 +1108,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>74083</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1570,233 +1286,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1164167</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1273831</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>13554</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="Рисунок 17" descr="Бесплатный PSD изолированный символ проверки">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7075ABB4-0AB1-42B9-94D9-63AEB6243D28}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect l="14991" t="15117" r="22046" b="15275"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="8932334" y="9609667"/>
-          <a:ext cx="109664" cy="117269"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1168400</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>46567</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1278064</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>167012</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="Рисунок 18" descr="Бесплатный PSD изолированный символ проверки">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2EA59A9-1CBE-4F65-8C0B-60E11C1AAFD7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect l="14991" t="15117" r="22046" b="15275"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="8936567" y="3676650"/>
-          <a:ext cx="109664" cy="117269"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1183218</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>50800</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1292882</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>169657</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="20" name="Рисунок 19" descr="Бесплатный PSD изолированный символ проверки">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FECD9F1D-5950-4776-A843-4F18714B4B71}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect l="14991" t="15117" r="22046" b="15275"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="8951385" y="4707467"/>
-          <a:ext cx="109664" cy="117269"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>112570</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1394114</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>90679</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Рисунок 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BFB8BDA-8504-EDD2-AE18-67F236F7E339}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="9490365"/>
-          <a:ext cx="7438159" cy="566928"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>203023</xdr:colOff>
       <xdr:row>0</xdr:row>
@@ -1822,7 +1311,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1836,7 +1325,137 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="203023" y="169332"/>
-          <a:ext cx="3374144" cy="561263"/>
+          <a:ext cx="3357916" cy="568319"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>74083</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="TextBox 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2844D812-3786-4267-A6FF-2D0BC3B761D9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="74083" y="9845675"/>
+          <a:ext cx="6374342" cy="327025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1400">
+              <a:latin typeface="+mn-lt"/>
+            </a:rPr>
+            <a:t>Срок действия Коммерческого предложения</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1400" baseline="0">
+              <a:latin typeface="+mn-lt"/>
+            </a:rPr>
+            <a:t>     </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1400">
+              <a:latin typeface="+mn-lt"/>
+            </a:rPr>
+            <a:t>дней</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>112570</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1394114</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>90679</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="Рисунок 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2A0562C-0278-46DF-9125-3820C79785E2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="9275620"/>
+          <a:ext cx="7442489" cy="597234"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2537,593 +2156,463 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:J108"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.5703125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="21" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.42578125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="51.85546875" style="4" customWidth="1"/>
-    <col min="9" max="9" width="3.42578125" style="4" customWidth="1"/>
-    <col min="10" max="10" width="38.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="1" width="3.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.5703125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="21" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.42578125" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D1"/>
       <c r="E1"/>
       <c r="F1"/>
     </row>
-    <row r="2" spans="1:10" ht="15.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="15.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D2"/>
       <c r="E2"/>
       <c r="F2"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D3"/>
       <c r="E3"/>
       <c r="F3"/>
-      <c r="H3" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="39" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D4"/>
       <c r="E4"/>
       <c r="F4"/>
-      <c r="H4" s="50"/>
-      <c r="J4" s="39"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D5"/>
       <c r="E5"/>
       <c r="F5"/>
-      <c r="H5" s="50"/>
-      <c r="J5" s="39"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D6"/>
       <c r="E6"/>
       <c r="F6"/>
-      <c r="H6" s="50"/>
-      <c r="J6" s="39"/>
-    </row>
-    <row r="7" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D7"/>
       <c r="E7"/>
       <c r="F7"/>
-      <c r="J7" s="40" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="6" t="s">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="J8" s="40"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="10"/>
-      <c r="H9" s="41"/>
-      <c r="J9" s="40"/>
-    </row>
-    <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="44" t="s">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="8"/>
+    </row>
+    <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="44"/>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="H10" s="19"/>
-      <c r="J10" s="40" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
-      <c r="B11" s="43" t="s">
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="13"/>
+      <c r="B11" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="H11" s="19"/>
-      <c r="J11" s="40"/>
-    </row>
-    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="45"/>
-      <c r="B12" s="45"/>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
-      <c r="H12" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="J12" s="40"/>
-    </row>
-    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="45"/>
-      <c r="B13" s="45"/>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="40"/>
-    </row>
-    <row r="14" spans="1:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="5"/>
-      <c r="B14" s="11" t="s">
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="42"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="42"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+    </row>
+    <row r="14" spans="1:7" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="B14" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="H14" s="19"/>
-      <c r="J14" s="40"/>
-    </row>
-    <row r="15" spans="1:10" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="12"/>
-      <c r="B15" s="42"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="I15" s="13"/>
-      <c r="J15" s="40"/>
-    </row>
-    <row r="16" spans="1:10" s="15" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="40"/>
-    </row>
-    <row r="17" spans="1:10" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="12"/>
-      <c r="B17" s="42"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
-      <c r="H17" s="41"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="40"/>
-    </row>
-    <row r="18" spans="1:10" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="40"/>
-    </row>
-    <row r="19" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="5"/>
-      <c r="B19" s="11" t="s">
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:7" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="10"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="14"/>
+    </row>
+    <row r="16" spans="1:7" s="13" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="10"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+    </row>
+    <row r="18" spans="1:6" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="4"/>
+      <c r="B19" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="H19" s="19"/>
-    </row>
-    <row r="20" spans="1:10" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="12"/>
-      <c r="B20" s="42"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
-      <c r="H20" s="41" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="H21" s="41"/>
-    </row>
-    <row r="22" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="12"/>
-      <c r="B22" s="42"/>
-      <c r="C22" s="42"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
-      <c r="H22" s="41"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
-    </row>
-    <row r="23" spans="1:10" s="13" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-    </row>
-    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B24" s="22" t="s">
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="10"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="10"/>
+      <c r="B22" s="33"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="33"/>
+    </row>
+    <row r="23" spans="1:6" s="11" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+    </row>
+    <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="46" t="s">
+      <c r="C24" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="D24" s="46" t="s">
+      <c r="D24" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="E24" s="46" t="s">
+      <c r="E24" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="F24" s="48" t="s">
+      <c r="F24" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="H24" s="51" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" s="13" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="18"/>
-      <c r="B25" s="23"/>
-      <c r="C25" s="47"/>
-      <c r="D25" s="47"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="49"/>
-      <c r="H25" s="53"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="7">
+    </row>
+    <row r="25" spans="1:6" s="11" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="53"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="39"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="54">
         <v>1</v>
       </c>
-      <c r="B26" s="28"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="29">
+      <c r="B26" s="55"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="21">
         <f>E26*D26</f>
         <v>0</v>
       </c>
-      <c r="H26" s="56" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
+    </row>
+    <row r="27" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="56">
         <v>2</v>
       </c>
-      <c r="B27" s="27"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="30">
-        <f t="shared" ref="F27:F37" si="0">E27*D27</f>
-        <v>0</v>
-      </c>
-      <c r="H27" s="57"/>
-    </row>
-    <row r="28" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
+      <c r="B27" s="57"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="22">
+        <f t="shared" ref="F27:F36" si="0">E27*D27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="56">
         <v>3</v>
       </c>
-      <c r="B28" s="27"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="30">
+      <c r="B28" s="57"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H28" s="57"/>
-    </row>
-    <row r="29" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
+    </row>
+    <row r="29" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="56">
         <v>4</v>
       </c>
-      <c r="B29" s="27"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="30">
+      <c r="B29" s="57"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H29" s="57"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="56">
         <v>5</v>
       </c>
-      <c r="B30" s="27"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="30">
+      <c r="B30" s="57"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H30" s="57"/>
-    </row>
-    <row r="31" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
+    </row>
+    <row r="31" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="56">
         <v>6</v>
       </c>
-      <c r="B31" s="27"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="30">
+      <c r="B31" s="57"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H31" s="57"/>
-    </row>
-    <row r="32" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
+    </row>
+    <row r="32" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="56">
         <v>7</v>
       </c>
-      <c r="B32" s="27"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="30">
+      <c r="B32" s="57"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H32" s="57"/>
-    </row>
-    <row r="33" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
+    </row>
+    <row r="33" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="56">
         <v>8</v>
       </c>
-      <c r="B33" s="27"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="30">
+      <c r="B33" s="57"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H33" s="57"/>
-    </row>
-    <row r="34" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
+    </row>
+    <row r="34" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="56">
         <v>9</v>
       </c>
-      <c r="B34" s="27"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="30">
+      <c r="B34" s="57"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H34" s="57"/>
-    </row>
-    <row r="35" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
+    </row>
+    <row r="35" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="56">
         <v>10</v>
       </c>
-      <c r="B35" s="27"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="30">
+      <c r="B35" s="57"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H35" s="57"/>
-    </row>
-    <row r="36" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
+    </row>
+    <row r="36" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="56">
         <v>11</v>
       </c>
-      <c r="B36" s="27"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="30">
+      <c r="B36" s="57"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H36" s="57"/>
-    </row>
-    <row r="37" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
-        <v>12</v>
-      </c>
-      <c r="B37" s="27"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="30">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H37" s="58"/>
-    </row>
-    <row r="38" spans="1:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="60"/>
-      <c r="B38" s="61"/>
-      <c r="C38" s="61"/>
-      <c r="D38" s="61"/>
-      <c r="E38" s="26" t="s">
+    </row>
+    <row r="37" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="34"/>
+      <c r="B37" s="35"/>
+      <c r="C37" s="35"/>
+      <c r="D37" s="35"/>
+      <c r="E37" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="F38" s="31">
-        <f>SUM(F26:F37)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="14" t="s">
+      <c r="F37" s="23">
+        <f>SUM(F26:F36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="H40" s="19"/>
-    </row>
-    <row r="41" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="12"/>
-      <c r="B41" s="42"/>
-      <c r="C41" s="42"/>
-      <c r="D41" s="42"/>
-      <c r="E41" s="42"/>
-      <c r="F41" s="42"/>
-      <c r="H41" s="41" t="s">
-        <v>26</v>
-      </c>
-      <c r="I41" s="13"/>
-      <c r="J41" s="13"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="H42" s="41"/>
-    </row>
-    <row r="43" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="12"/>
-      <c r="B43" s="42"/>
-      <c r="C43" s="42"/>
-      <c r="D43" s="42"/>
-      <c r="E43" s="42"/>
-      <c r="F43" s="42"/>
-      <c r="H43" s="41"/>
-      <c r="I43" s="13"/>
-      <c r="J43" s="13"/>
-    </row>
-    <row r="44" spans="1:10" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="4"/>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="H44" s="59" t="s">
-        <v>30</v>
-      </c>
-      <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
-    </row>
-    <row r="45" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H45" s="41"/>
-    </row>
-    <row r="46" spans="1:10" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="54"/>
-      <c r="B46" s="54"/>
-      <c r="C46" s="54"/>
-      <c r="D46" s="54"/>
-      <c r="E46" s="54"/>
-      <c r="F46" s="54"/>
-      <c r="H46" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="I46" s="4"/>
-      <c r="J46" s="4"/>
-    </row>
-    <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="54"/>
-      <c r="B47" s="54"/>
-      <c r="C47" s="54"/>
-      <c r="D47" s="54"/>
-      <c r="E47" s="54"/>
-      <c r="F47" s="54"/>
-      <c r="H47" s="41"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="54"/>
-      <c r="B48" s="54"/>
-      <c r="C48" s="54"/>
-      <c r="D48" s="54"/>
-      <c r="E48" s="54"/>
-      <c r="F48" s="54"/>
-      <c r="H48" s="41"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H49" s="19"/>
-    </row>
-    <row r="50" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="5" t="s">
+    </row>
+    <row r="40" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="10"/>
+      <c r="B40" s="33"/>
+      <c r="C40" s="33"/>
+      <c r="D40" s="33"/>
+      <c r="E40" s="33"/>
+      <c r="F40" s="33"/>
+    </row>
+    <row r="42" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="10"/>
+      <c r="B42" s="33"/>
+      <c r="C42" s="33"/>
+      <c r="D42" s="33"/>
+      <c r="E42" s="33"/>
+      <c r="F42" s="33"/>
+    </row>
+    <row r="43" spans="1:6" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+    </row>
+    <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:6" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="31"/>
+      <c r="B45" s="31"/>
+      <c r="C45" s="31"/>
+      <c r="D45" s="31"/>
+      <c r="E45" s="31"/>
+      <c r="F45" s="31"/>
+    </row>
+    <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="31"/>
+      <c r="B46" s="31"/>
+      <c r="C46" s="31"/>
+      <c r="D46" s="31"/>
+      <c r="E46" s="31"/>
+      <c r="F46" s="31"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="31"/>
+      <c r="B47" s="31"/>
+      <c r="C47" s="31"/>
+      <c r="D47" s="31"/>
+      <c r="E47" s="31"/>
+      <c r="F47" s="31"/>
+    </row>
+    <row r="49" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H50" s="51" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B51" s="21" t="s">
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B50" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="H51" s="52"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B52" s="5" t="s">
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B51" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="H52" s="52"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B53" s="55" t="s">
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B52" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="C53" s="55"/>
-      <c r="H53" s="52"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B54" s="55" t="s">
+      <c r="C52" s="32"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B53" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="C54" s="55"/>
-      <c r="H54" s="53"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H55" s="20" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C53" s="32"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55"/>
+      <c r="B55"/>
+      <c r="C55"/>
+      <c r="D55"/>
+      <c r="E55"/>
+      <c r="F55"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56"/>
       <c r="B56"/>
       <c r="C56"/>
@@ -3131,7 +2620,7 @@
       <c r="E56"/>
       <c r="F56"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57"/>
       <c r="B57"/>
       <c r="C57"/>
@@ -3139,15 +2628,16 @@
       <c r="E57"/>
       <c r="F57"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58"/>
       <c r="B58"/>
       <c r="C58"/>
       <c r="D58"/>
       <c r="E58"/>
       <c r="F58"/>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G58"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59"/>
       <c r="B59"/>
       <c r="C59"/>
@@ -3156,7 +2646,7 @@
       <c r="F59"/>
       <c r="G59"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60"/>
       <c r="B60"/>
       <c r="C60"/>
@@ -3165,7 +2655,7 @@
       <c r="F60"/>
       <c r="G60"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61"/>
       <c r="B61"/>
       <c r="C61"/>
@@ -3174,7 +2664,7 @@
       <c r="F61"/>
       <c r="G61"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62"/>
       <c r="B62"/>
       <c r="C62"/>
@@ -3183,7 +2673,7 @@
       <c r="F62"/>
       <c r="G62"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63"/>
       <c r="B63"/>
       <c r="C63"/>
@@ -3192,7 +2682,7 @@
       <c r="F63"/>
       <c r="G63"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64"/>
       <c r="B64"/>
       <c r="C64"/>
@@ -3562,12 +3052,6 @@
       <c r="G104"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105"/>
-      <c r="B105"/>
-      <c r="C105"/>
-      <c r="D105"/>
-      <c r="E105"/>
-      <c r="F105"/>
       <c r="G105"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -3576,47 +3060,28 @@
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G107"/>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G108"/>
-    </row>
   </sheetData>
-  <mergeCells count="36">
-    <mergeCell ref="H50:H54"/>
-    <mergeCell ref="A48:F48"/>
+  <mergeCells count="20">
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="B52:C52"/>
     <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="H20:H22"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="H26:H37"/>
-    <mergeCell ref="H41:H43"/>
-    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="A45:F45"/>
     <mergeCell ref="A46:F46"/>
-    <mergeCell ref="H46:H48"/>
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="H3:H6"/>
-    <mergeCell ref="J3:J6"/>
-    <mergeCell ref="J7:J9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="H12:H13"/>
     <mergeCell ref="B20:F20"/>
-    <mergeCell ref="H15:H17"/>
     <mergeCell ref="B15:F15"/>
-    <mergeCell ref="J10:J12"/>
-    <mergeCell ref="J13:J15"/>
-    <mergeCell ref="J16:J18"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="A13:F13"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="C24:C25"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.11811023622047245" footer="0.19685039370078741"/>
@@ -3633,17 +3098,17 @@
   <dimension ref="A1:J109"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.140625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="8" style="4" customWidth="1"/>
-    <col min="4" max="4" width="9.5703125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="7.140625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16.28515625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="19.7109375" style="4" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="1" width="3.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="8" style="3" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="7.140625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="16.28515625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="19.7109375" style="3" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3703,628 +3168,628 @@
       <c r="I7"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="6" t="s">
-        <v>40</v>
+      <c r="B8" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" x14ac:dyDescent="0.25">
-      <c r="A10" s="44" t="s">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+    </row>
+    <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="44"/>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41"/>
     </row>
     <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
-      <c r="B11" s="43" t="s">
+      <c r="A11" s="13"/>
+      <c r="B11" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="43"/>
-      <c r="I11" s="43"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="40"/>
+      <c r="I11" s="40"/>
     </row>
     <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="45"/>
-      <c r="B12" s="45"/>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
+      <c r="A12" s="42"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="45"/>
-      <c r="B13" s="45"/>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="45"/>
+      <c r="A13" s="42"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
     </row>
     <row r="14" spans="1:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="5"/>
-      <c r="B14" s="11" t="s">
+      <c r="A14" s="4"/>
+      <c r="B14" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-    </row>
-    <row r="15" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="12"/>
-      <c r="B15" s="42"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="42"/>
-      <c r="J15" s="16"/>
-    </row>
-    <row r="16" spans="1:10" s="15" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-    </row>
-    <row r="17" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="12"/>
-      <c r="B17" s="42"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="42"/>
-    </row>
-    <row r="18" spans="1:9" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-    </row>
-    <row r="19" spans="1:9" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="5"/>
-      <c r="B19" s="11" t="s">
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+    </row>
+    <row r="15" spans="1:10" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="10"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="14"/>
+    </row>
+    <row r="16" spans="1:10" s="13" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+    </row>
+    <row r="17" spans="1:9" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="10"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="33"/>
+    </row>
+    <row r="18" spans="1:9" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+    </row>
+    <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="4"/>
+      <c r="B19" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-    </row>
-    <row r="20" spans="1:9" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="12"/>
-      <c r="B20" s="42"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="42"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+    </row>
+    <row r="20" spans="1:9" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="10"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="33"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
     </row>
     <row r="22" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="12"/>
-      <c r="B22" s="42"/>
-      <c r="C22" s="42"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="42"/>
-      <c r="I22" s="42"/>
-    </row>
-    <row r="23" spans="1:9" s="13" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="4"/>
-      <c r="B23" s="35"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
+      <c r="A22" s="10"/>
+      <c r="B22" s="33"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="33"/>
+      <c r="H22" s="33"/>
+      <c r="I22" s="33"/>
+    </row>
+    <row r="23" spans="1:9" s="11" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="67" t="s">
-        <v>0</v>
-      </c>
-      <c r="B24" s="46" t="s">
+      <c r="A24" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="46" t="s">
+      <c r="C24" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="D24" s="46" t="s">
+      <c r="D24" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="E24" s="46" t="s">
+      <c r="E24" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="F24" s="46" t="s">
+      <c r="F24" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="G24" s="62" t="s">
-        <v>36</v>
-      </c>
-      <c r="H24" s="63"/>
-      <c r="I24" s="48" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" s="13" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="68"/>
-      <c r="B25" s="47"/>
-      <c r="C25" s="47"/>
-      <c r="D25" s="47"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="47"/>
-      <c r="G25" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="H25" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="I25" s="49"/>
-    </row>
-    <row r="26" spans="1:9" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="36">
+      <c r="G24" s="58" t="s">
+        <v>21</v>
+      </c>
+      <c r="H24" s="59"/>
+      <c r="I24" s="38" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" s="11" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="50"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="H25" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="I25" s="39"/>
+    </row>
+    <row r="26" spans="1:9" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="28">
         <v>1</v>
       </c>
-      <c r="B26" s="37"/>
-      <c r="C26" s="37"/>
-      <c r="D26" s="37"/>
-      <c r="E26" s="37"/>
-      <c r="F26" s="32">
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="24">
         <f>D26*E26</f>
         <v>0</v>
       </c>
-      <c r="G26" s="33">
+      <c r="G26" s="25">
         <v>0.12</v>
       </c>
-      <c r="H26" s="3">
+      <c r="H26" s="2">
         <f>F26*0.12</f>
         <v>0</v>
       </c>
-      <c r="I26" s="32">
+      <c r="I26" s="24">
         <f>F26+H26</f>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="36">
+    <row r="27" spans="1:9" s="11" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="28">
         <v>2</v>
       </c>
-      <c r="B27" s="37"/>
-      <c r="C27" s="37"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="32">
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="24">
         <f t="shared" ref="F27:F36" si="0">D27*E27</f>
         <v>0</v>
       </c>
-      <c r="G27" s="33">
+      <c r="G27" s="25">
         <v>0.12</v>
       </c>
-      <c r="H27" s="3">
+      <c r="H27" s="2">
         <f t="shared" ref="H27:H36" si="1">F27*0.12</f>
         <v>0</v>
       </c>
-      <c r="I27" s="32">
+      <c r="I27" s="24">
         <f t="shared" ref="I27:I36" si="2">F27+H27</f>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="36">
+    <row r="28" spans="1:9" s="11" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="28">
         <v>3</v>
       </c>
-      <c r="B28" s="37"/>
-      <c r="C28" s="37"/>
-      <c r="D28" s="37"/>
-      <c r="E28" s="37"/>
-      <c r="F28" s="32">
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G28" s="33">
+      <c r="G28" s="25">
         <v>0.12</v>
       </c>
-      <c r="H28" s="3">
+      <c r="H28" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I28" s="32">
+      <c r="I28" s="24">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="36">
+    <row r="29" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="28">
         <v>4</v>
       </c>
-      <c r="B29" s="37"/>
-      <c r="C29" s="37"/>
-      <c r="D29" s="37"/>
-      <c r="E29" s="37"/>
-      <c r="F29" s="32">
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G29" s="33">
+      <c r="G29" s="25">
         <v>0.12</v>
       </c>
-      <c r="H29" s="3">
+      <c r="H29" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I29" s="32">
+      <c r="I29" s="24">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="36">
+    <row r="30" spans="1:9" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="28">
         <v>5</v>
       </c>
-      <c r="B30" s="37"/>
-      <c r="C30" s="37"/>
-      <c r="D30" s="37"/>
-      <c r="E30" s="37"/>
-      <c r="F30" s="32">
+      <c r="B30" s="29"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="24">
         <f t="shared" ref="F30" si="3">D30*E30</f>
         <v>0</v>
       </c>
-      <c r="G30" s="33">
+      <c r="G30" s="25">
         <v>0.12</v>
       </c>
-      <c r="H30" s="3">
+      <c r="H30" s="2">
         <f t="shared" ref="H30" si="4">F30*0.12</f>
         <v>0</v>
       </c>
-      <c r="I30" s="32">
+      <c r="I30" s="24">
         <f t="shared" ref="I30" si="5">F30+H30</f>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="36">
+    <row r="31" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="28">
         <v>6</v>
       </c>
-      <c r="B31" s="37"/>
-      <c r="C31" s="37"/>
-      <c r="D31" s="37"/>
-      <c r="E31" s="37"/>
-      <c r="F31" s="32">
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="24">
         <f t="shared" ref="F31" si="6">D31*E31</f>
         <v>0</v>
       </c>
-      <c r="G31" s="33">
+      <c r="G31" s="25">
         <v>0.12</v>
       </c>
-      <c r="H31" s="3">
+      <c r="H31" s="2">
         <f t="shared" ref="H31" si="7">F31*0.12</f>
         <v>0</v>
       </c>
-      <c r="I31" s="32">
+      <c r="I31" s="24">
         <f t="shared" ref="I31" si="8">F31+H31</f>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="36">
+    <row r="32" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="28">
         <v>7</v>
       </c>
-      <c r="B32" s="37"/>
-      <c r="C32" s="37"/>
-      <c r="D32" s="37"/>
-      <c r="E32" s="37"/>
-      <c r="F32" s="32">
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="24">
         <f t="shared" ref="F32" si="9">D32*E32</f>
         <v>0</v>
       </c>
-      <c r="G32" s="33">
+      <c r="G32" s="25">
         <v>0.12</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="2">
         <f t="shared" ref="H32" si="10">F32*0.12</f>
         <v>0</v>
       </c>
-      <c r="I32" s="32">
+      <c r="I32" s="24">
         <f t="shared" ref="I32" si="11">F32+H32</f>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="36">
+    <row r="33" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="28">
         <v>8</v>
       </c>
-      <c r="B33" s="37"/>
-      <c r="C33" s="37"/>
-      <c r="D33" s="37"/>
-      <c r="E33" s="37"/>
-      <c r="F33" s="32">
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="24">
         <f t="shared" ref="F33" si="12">D33*E33</f>
         <v>0</v>
       </c>
-      <c r="G33" s="33">
+      <c r="G33" s="25">
         <v>0.12</v>
       </c>
-      <c r="H33" s="3">
+      <c r="H33" s="2">
         <f t="shared" ref="H33" si="13">F33*0.12</f>
         <v>0</v>
       </c>
-      <c r="I33" s="32">
+      <c r="I33" s="24">
         <f t="shared" ref="I33" si="14">F33+H33</f>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:9" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="36">
+    <row r="34" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="28">
         <v>9</v>
       </c>
-      <c r="B34" s="37"/>
-      <c r="C34" s="37"/>
-      <c r="D34" s="37"/>
-      <c r="E34" s="37"/>
-      <c r="F34" s="32">
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="24">
         <f t="shared" ref="F34" si="15">D34*E34</f>
         <v>0</v>
       </c>
-      <c r="G34" s="33">
+      <c r="G34" s="25">
         <v>0.12</v>
       </c>
-      <c r="H34" s="3">
+      <c r="H34" s="2">
         <f t="shared" ref="H34" si="16">F34*0.12</f>
         <v>0</v>
       </c>
-      <c r="I34" s="32">
+      <c r="I34" s="24">
         <f t="shared" ref="I34" si="17">F34+H34</f>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="36">
+    <row r="35" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="28">
         <v>10</v>
       </c>
-      <c r="B35" s="37"/>
-      <c r="C35" s="37"/>
-      <c r="D35" s="37"/>
-      <c r="E35" s="37"/>
-      <c r="F35" s="32">
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="24">
         <f t="shared" ref="F35" si="18">D35*E35</f>
         <v>0</v>
       </c>
-      <c r="G35" s="33">
+      <c r="G35" s="25">
         <v>0.12</v>
       </c>
-      <c r="H35" s="3">
+      <c r="H35" s="2">
         <f t="shared" ref="H35" si="19">F35*0.12</f>
         <v>0</v>
       </c>
-      <c r="I35" s="32">
+      <c r="I35" s="24">
         <f t="shared" ref="I35" si="20">F35+H35</f>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="36">
+    <row r="36" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="28">
         <v>11</v>
       </c>
-      <c r="B36" s="37"/>
-      <c r="C36" s="37"/>
-      <c r="D36" s="37"/>
-      <c r="E36" s="37"/>
-      <c r="F36" s="32">
+      <c r="B36" s="29"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="29"/>
+      <c r="E36" s="29"/>
+      <c r="F36" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G36" s="33">
+      <c r="G36" s="25">
         <v>0.12</v>
       </c>
-      <c r="H36" s="3">
+      <c r="H36" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I36" s="32">
+      <c r="I36" s="24">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="64" t="s">
+    <row r="37" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="B37" s="65"/>
-      <c r="C37" s="65"/>
-      <c r="D37" s="65"/>
-      <c r="E37" s="65"/>
-      <c r="F37" s="65"/>
-      <c r="G37" s="65"/>
-      <c r="H37" s="66"/>
-      <c r="I37" s="34">
+      <c r="B37" s="47"/>
+      <c r="C37" s="47"/>
+      <c r="D37" s="47"/>
+      <c r="E37" s="47"/>
+      <c r="F37" s="47"/>
+      <c r="G37" s="47"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="26">
         <f>SUM(I26:I36)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B39" s="14" t="s">
+    <row r="39" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="12" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="12"/>
-      <c r="B40" s="72"/>
-      <c r="C40" s="72"/>
-      <c r="D40" s="72"/>
-      <c r="E40" s="72"/>
-      <c r="F40" s="72"/>
-      <c r="G40" s="72"/>
-      <c r="H40" s="72"/>
-      <c r="I40" s="72"/>
-    </row>
-    <row r="41" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="12"/>
-      <c r="B41" s="21"/>
-      <c r="C41" s="70"/>
-      <c r="D41" s="70"/>
-      <c r="E41" s="71"/>
-      <c r="F41" s="71"/>
-      <c r="G41" s="71"/>
-      <c r="H41" s="71"/>
-      <c r="I41" s="21"/>
-    </row>
-    <row r="42" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="12"/>
-      <c r="B42" s="12"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12"/>
-      <c r="H42" s="12"/>
-      <c r="I42" s="12"/>
-    </row>
-    <row r="43" spans="1:9" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="4"/>
-      <c r="B43" s="69" t="s">
-        <v>41</v>
-      </c>
-      <c r="C43" s="69"/>
-      <c r="D43" s="69"/>
-      <c r="E43" s="69"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-    </row>
-    <row r="44" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="69"/>
-      <c r="C44" s="69"/>
-      <c r="D44" s="69"/>
-      <c r="E44" s="69"/>
-    </row>
-    <row r="45" spans="1:9" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="54"/>
-      <c r="B45" s="54"/>
-      <c r="C45" s="54"/>
-      <c r="D45" s="54"/>
-      <c r="E45" s="54"/>
-      <c r="F45" s="54"/>
-      <c r="G45" s="54"/>
-      <c r="H45" s="54"/>
-      <c r="I45" s="54"/>
+      <c r="A40" s="10"/>
+      <c r="B40" s="45"/>
+      <c r="C40" s="45"/>
+      <c r="D40" s="45"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="45"/>
+      <c r="G40" s="45"/>
+      <c r="H40" s="45"/>
+      <c r="I40" s="45"/>
+    </row>
+    <row r="41" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="10"/>
+      <c r="B41" s="15"/>
+      <c r="C41" s="43"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="44"/>
+      <c r="F41" s="44"/>
+      <c r="G41" s="44"/>
+      <c r="H41" s="44"/>
+      <c r="I41" s="15"/>
+    </row>
+    <row r="42" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="10"/>
+      <c r="B42" s="10"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="10"/>
+    </row>
+    <row r="43" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="3"/>
+      <c r="B43" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="C43" s="51"/>
+      <c r="D43" s="51"/>
+      <c r="E43" s="51"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
+    </row>
+    <row r="44" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="51"/>
+      <c r="C44" s="51"/>
+      <c r="D44" s="51"/>
+      <c r="E44" s="51"/>
+    </row>
+    <row r="45" spans="1:9" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="31"/>
+      <c r="B45" s="31"/>
+      <c r="C45" s="31"/>
+      <c r="D45" s="31"/>
+      <c r="E45" s="31"/>
+      <c r="F45" s="31"/>
+      <c r="G45" s="31"/>
+      <c r="H45" s="31"/>
+      <c r="I45" s="31"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="54"/>
-      <c r="B46" s="54"/>
-      <c r="C46" s="54"/>
-      <c r="D46" s="54"/>
-      <c r="E46" s="54"/>
-      <c r="F46" s="54"/>
-      <c r="G46" s="54"/>
-      <c r="H46" s="54"/>
-      <c r="I46" s="54"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="54"/>
-      <c r="B47" s="54"/>
-      <c r="C47" s="54"/>
-      <c r="D47" s="54"/>
-      <c r="E47" s="54"/>
-      <c r="F47" s="54"/>
-      <c r="G47" s="54"/>
-      <c r="H47" s="54"/>
-      <c r="I47" s="54"/>
-    </row>
-    <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="5" t="s">
+      <c r="A46" s="31"/>
+      <c r="B46" s="31"/>
+      <c r="C46" s="31"/>
+      <c r="D46" s="31"/>
+      <c r="E46" s="31"/>
+      <c r="F46" s="31"/>
+      <c r="G46" s="31"/>
+      <c r="H46" s="31"/>
+      <c r="I46" s="31"/>
+    </row>
+    <row r="47" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="31"/>
+      <c r="B47" s="31"/>
+      <c r="C47" s="31"/>
+      <c r="D47" s="31"/>
+      <c r="E47" s="31"/>
+      <c r="F47" s="31"/>
+      <c r="G47" s="31"/>
+      <c r="H47" s="31"/>
+      <c r="I47" s="31"/>
+    </row>
+    <row r="49" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B50" s="55" t="s">
+      <c r="B50" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="C50" s="55"/>
+      <c r="C50" s="32"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B51" s="5" t="s">
+      <c r="B51" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B52" s="55" t="s">
+      <c r="B52" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="C52" s="55"/>
-      <c r="D52" s="55"/>
+      <c r="C52" s="32"/>
+      <c r="D52" s="32"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B53" s="55" t="s">
+      <c r="B53" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="C53" s="55"/>
-      <c r="D53" s="55"/>
+      <c r="C53" s="32"/>
+      <c r="D53" s="32"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="I54" s="4" t="s">
+      <c r="I54" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4936,18 +4401,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B22:I22"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="B40:I40"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="B17:I17"/>
-    <mergeCell ref="A10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B15:I15"/>
-    <mergeCell ref="B20:I20"/>
-    <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A13:I13"/>
     <mergeCell ref="B52:D52"/>
     <mergeCell ref="B53:D53"/>
     <mergeCell ref="G24:H24"/>
@@ -4964,6 +4417,18 @@
     <mergeCell ref="A46:I46"/>
     <mergeCell ref="A47:I47"/>
     <mergeCell ref="B43:E44"/>
+    <mergeCell ref="B17:I17"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B15:I15"/>
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="B22:I22"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="B40:I40"/>
+    <mergeCell ref="G41:H41"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.11811023622047245" footer="0.19685039370078741"/>

--- a/public/templates/kp-template-11.xlsx
+++ b/public/templates/kp-template-11.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mp-calc-2.0\price-calc\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A1F3D46-8650-4BED-B1E1-FDFD5486289B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D989325-A430-4600-BAF4-A3154BC6EE0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="23160" windowHeight="11910" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="КП-1 (с НДС) RUS" sheetId="16" r:id="rId1"/>
     <sheet name="КП-2 (со СКИДКОЙ) RUS" sheetId="19" r:id="rId2"/>
-    <sheet name="Лого" sheetId="17" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'КП-1 (с НДС) RUS'!$A$1:$F$54</definedName>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="31">
   <si>
     <t>№</t>
   </si>
@@ -144,6 +143,26 @@
   <si>
     <t>Срок действия Коммерческого предложения  10  дней</t>
   </si>
+  <si>
+    <t xml:space="preserve">☐ Фундамент    ☐ Фасад    ☐ СК    ☐ ЛКМ    ☐ Звукоизоляция    ☐ Линейный водоотвод   
+☐ Мансарда    ☐ Терасса    ☐ ПК    ☐ Полы    ☐ Опалубочная система    </t>
+  </si>
+  <si>
+    <t>☐ Узбекистан    ☐ Германия    ☐ Грузия    ☐ Швейцария    ☐ Казахстан    ☐ Россия    ☐ Бельгия    ☐ Дания
+☐ Финляндия    ☐ Франция    ☐ Китай    ☐ Туркменистан    ☐ Беларусь    ☐ Италия    ☐ Польша    ☐ Турция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">☐ В наличии    ☐ Комплексность    ☐ Временное хранение    ☐ Скидка    ☐ Доствка       
+☐ Шеф. Монтаж    ☐ Эксклюзивность    ☐ Ускоренная поставка    ☐ Доп. скидка    ☐ PMG    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ООО «TEXNO DAT»
+100033, Республика Узбекистан, г. Ташкент, 
+Бектемирский р-н, ул. Олтинтопган, дом 25Д
+Тел.: +99871291-37-75.Р/с 2020 8000 3048 2507 1001
+в ОПЕРУ АКБ «ASIA ALLIANCE BANK», МФО 01095
+                                       ИНН 301262117 ОКЭД 46730 </t>
+  </si>
 </sst>
 </file>
 
@@ -154,7 +173,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _₽_-;\-* #,##0.00\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -287,6 +306,40 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -658,7 +711,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -688,9 +741,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -750,21 +800,45 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -777,22 +851,10 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -813,29 +875,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -861,429 +920,6 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>3055071</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>40748</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>4185</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>79374</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="TextBox 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A08B13BD-3D0C-A588-4778-BB101C270558}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3264621" y="40748"/>
-          <a:ext cx="4188114" cy="1553101"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="uz-Cyrl-UZ" sz="1400" b="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>ООО «</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>TEXNO DAT»</a:t>
-          </a:r>
-          <a:endParaRPr lang="ru-RU" sz="1400" b="1" baseline="0">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:latin typeface="+mn-lt"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="uz-Cyrl-UZ" sz="1400" b="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>100033, Республика Узбекистан, г. Ташкент, </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="uz-Cyrl-UZ" sz="1400" b="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>Бектемирский р-н, ул. Олтинтопган, дом 25Д</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="uz-Cyrl-UZ" sz="1400" b="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>Тел.: +99871291-37-75.Р/с 2020 8000 3048 2507 1001</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="uz-Cyrl-UZ" sz="1400" b="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>в ОПЕРУ АКБ «</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>ASIA ALLIANCE BANK», </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="uz-Cyrl-UZ" sz="1400" b="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>МФО 01095</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="uz-Cyrl-UZ" sz="1400" b="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>                                       ИНН 301262117 ОКЭД 46730 </a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>74083</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="TextBox 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFC53FC5-A261-4CE6-BDB0-C6513216ED29}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="74083" y="9853083"/>
-          <a:ext cx="5048249" cy="317500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="ru-RU" sz="1400">
-              <a:latin typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>Срок действия Коммерческого предложения</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ru-RU" sz="1400" baseline="0">
-              <a:latin typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>     </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ru-RU" sz="1400">
-              <a:latin typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>дней</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>74083</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="TextBox 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FE0A377-8C7C-40DD-AABF-2C41029E77F3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="74083" y="10074275"/>
-          <a:ext cx="5040842" cy="317500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="ru-RU" sz="1400">
-              <a:latin typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>Срок действия Коммерческого предложения</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400">
-              <a:latin typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>     </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ru-RU" sz="1400">
-              <a:latin typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>дней</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>44952</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>52917</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Рисунок 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B49A1E7-8A74-4EC4-A980-20D9368077B8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="3690429"/>
-          <a:ext cx="7446818" cy="596783"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>97192</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1394114</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>31749</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="Рисунок 14">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A025B267-4723-4FCE-AC15-D750C5E28A2C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="4764442"/>
-          <a:ext cx="7438159" cy="523375"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -1311,7 +947,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1334,404 +970,11 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>74083</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>400050</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="TextBox 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2844D812-3786-4267-A6FF-2D0BC3B761D9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="74083" y="9845675"/>
-          <a:ext cx="6374342" cy="327025"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="ru-RU" sz="1400">
-              <a:latin typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>Срок действия Коммерческого предложения</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ru-RU" sz="1400" baseline="0">
-              <a:latin typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>     </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ru-RU" sz="1400">
-              <a:latin typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>дней</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>112570</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1394114</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>90679</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="Рисунок 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2A0562C-0278-46DF-9125-3820C79785E2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="9275620"/>
-          <a:ext cx="7442489" cy="597234"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>40189</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>2218</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>40188</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Рисунок 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{741C20EB-3AEF-4466-B41E-FD507C53B61F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="2931307"/>
-          <a:ext cx="7823924" cy="605116"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>39687</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>37661</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>153437</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Рисунок 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BF09131-246C-41BB-89FD-C8C1E8AC3C57}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="39687" y="4695386"/>
-          <a:ext cx="7618413" cy="506301"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>2515321</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>40748</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>1073727</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>79374</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="TextBox 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C34432F9-B864-4FD4-AED6-5CD4BDB7E452}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2740457" y="40748"/>
-          <a:ext cx="5303838" cy="1523661"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="uz-Cyrl-UZ" sz="1400" b="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>ООО «</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>TEXNO DAT»</a:t>
-          </a:r>
-          <a:endParaRPr lang="ru-RU" sz="1400" b="1" baseline="0">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:latin typeface="+mn-lt"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="uz-Cyrl-UZ" sz="1400" b="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>100033, Республика Узбекистан, г. Ташкент, </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="uz-Cyrl-UZ" sz="1400" b="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>Бектемирский р-н, ул. Олтинтопган, дом 25Д</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="uz-Cyrl-UZ" sz="1400" b="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>Тел.: +99871291-37-75.Р/с 2020 8000 3048 2507 1001</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="uz-Cyrl-UZ" sz="1400" b="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>в ОПЕРУ АКБ «</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>ASIA ALLIANCE BANK», </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="uz-Cyrl-UZ" sz="1400" b="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>МФО 01095</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="uz-Cyrl-UZ" sz="1400" b="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>                                       ИНН 301262117 ОКЭД 46730 </a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -1759,7 +1002,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1774,111 +1017,6 @@
         <a:xfrm>
           <a:off x="228600" y="184150"/>
           <a:ext cx="3375732" cy="559675"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>1080416</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>176798</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Рисунок 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C48BCF48-8500-4D41-A8F7-6DD2543CE828}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="5817577"/>
-          <a:ext cx="7894454" cy="594433"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>28573</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>47624</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>600074</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Рисунок 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8BD127EA-C990-E777-C4FD-E322044A774E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="28573" y="47624"/>
-          <a:ext cx="6057901" cy="9448801"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2164,50 +1302,63 @@
     <col min="3" max="3" width="8.5703125" style="3" customWidth="1"/>
     <col min="4" max="4" width="10.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.140625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="21" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.28515625" style="3" customWidth="1"/>
     <col min="7" max="7" width="6.42578125" style="3" customWidth="1"/>
     <col min="8" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D1"/>
-      <c r="E1"/>
-      <c r="F1"/>
+      <c r="C1" s="58" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
     </row>
     <row r="2" spans="1:7" ht="15.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D2"/>
-      <c r="E2"/>
-      <c r="F2"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D3"/>
-      <c r="E3"/>
-      <c r="F3"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D4"/>
-      <c r="E4"/>
-      <c r="F4"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D5"/>
-      <c r="E5"/>
-      <c r="F5"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D6"/>
-      <c r="E6"/>
-      <c r="F6"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
     </row>
     <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D7"/>
-      <c r="E7"/>
-      <c r="F7"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="58"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
         <v>19</v>
       </c>
+      <c r="C8" s="58"/>
+      <c r="D8" s="58"/>
+      <c r="E8" s="58"/>
+      <c r="F8" s="58"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
@@ -2228,7 +1379,7 @@
       <c r="F10" s="41"/>
     </row>
     <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
+      <c r="A11" s="12"/>
       <c r="B11" s="40" t="s">
         <v>14</v>
       </c>
@@ -2264,31 +1415,33 @@
       <c r="F14" s="4"/>
     </row>
     <row r="15" spans="1:7" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="10"/>
-      <c r="B15" s="33"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="14"/>
-    </row>
-    <row r="16" spans="1:7" s="13" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
+      <c r="A15" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="55"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="55"/>
+      <c r="E15" s="55"/>
+      <c r="F15" s="55"/>
+      <c r="G15" s="13"/>
+    </row>
+    <row r="16" spans="1:7" s="12" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="55"/>
+      <c r="B16" s="55"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="55"/>
+      <c r="E16" s="55"/>
+      <c r="F16" s="55"/>
     </row>
     <row r="17" spans="1:6" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="10"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
-    </row>
-    <row r="18" spans="1:6" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="55"/>
+      <c r="B17" s="55"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="55"/>
+      <c r="F17" s="55"/>
+    </row>
+    <row r="18" spans="1:6" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -2306,31 +1459,33 @@
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
     </row>
-    <row r="20" spans="1:6" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="10"/>
-      <c r="B20" s="33"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
+    <row r="20" spans="1:6" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="56" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="56"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="56"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
+      <c r="A21" s="56"/>
+      <c r="B21" s="56"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
     </row>
     <row r="22" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="10"/>
-      <c r="B22" s="33"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-    </row>
-    <row r="23" spans="1:6" s="11" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="56"/>
+      <c r="B22" s="56"/>
+      <c r="C22" s="56"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="56"/>
+      <c r="F22" s="56"/>
+    </row>
+    <row r="23" spans="1:6" s="10" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -2339,243 +1494,260 @@
       <c r="F23" s="3"/>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="B24" s="16" t="s">
+      <c r="A24" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="36" t="s">
+      <c r="C24" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="D24" s="36" t="s">
+      <c r="D24" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="E24" s="36" t="s">
+      <c r="E24" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="F24" s="38" t="s">
+      <c r="F24" s="45" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:6" s="11" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="53"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="37"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="39"/>
+    <row r="25" spans="1:6" s="10" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="31"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="44"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="46"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="54">
+      <c r="A26" s="32">
         <v>1</v>
       </c>
-      <c r="B26" s="55"/>
+      <c r="B26" s="33"/>
       <c r="C26" s="6"/>
       <c r="D26" s="7"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="21">
+      <c r="E26" s="18"/>
+      <c r="F26" s="20">
         <f>E26*D26</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="56">
+      <c r="A27" s="34">
         <v>2</v>
       </c>
-      <c r="B27" s="57"/>
+      <c r="B27" s="35"/>
       <c r="C27" s="1"/>
       <c r="D27" s="2"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="22">
+      <c r="E27" s="17"/>
+      <c r="F27" s="21">
         <f t="shared" ref="F27:F36" si="0">E27*D27</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="56">
+      <c r="A28" s="34">
         <v>3</v>
       </c>
-      <c r="B28" s="57"/>
+      <c r="B28" s="35"/>
       <c r="C28" s="1"/>
       <c r="D28" s="2"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="22">
+      <c r="E28" s="17"/>
+      <c r="F28" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="56">
+      <c r="A29" s="34">
         <v>4</v>
       </c>
-      <c r="B29" s="57"/>
+      <c r="B29" s="35"/>
       <c r="C29" s="1"/>
       <c r="D29" s="2"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="22">
+      <c r="E29" s="17"/>
+      <c r="F29" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="56">
+      <c r="A30" s="34">
         <v>5</v>
       </c>
-      <c r="B30" s="57"/>
+      <c r="B30" s="35"/>
       <c r="C30" s="1"/>
       <c r="D30" s="2"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="22">
+      <c r="E30" s="17"/>
+      <c r="F30" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="56">
+      <c r="A31" s="34">
         <v>6</v>
       </c>
-      <c r="B31" s="57"/>
+      <c r="B31" s="35"/>
       <c r="C31" s="1"/>
       <c r="D31" s="2"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="22">
+      <c r="E31" s="17"/>
+      <c r="F31" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="56">
+      <c r="A32" s="34">
         <v>7</v>
       </c>
-      <c r="B32" s="57"/>
+      <c r="B32" s="35"/>
       <c r="C32" s="1"/>
       <c r="D32" s="2"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="22">
+      <c r="E32" s="17"/>
+      <c r="F32" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="56">
+      <c r="A33" s="34">
         <v>8</v>
       </c>
-      <c r="B33" s="57"/>
+      <c r="B33" s="35"/>
       <c r="C33" s="1"/>
       <c r="D33" s="2"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="22">
+      <c r="E33" s="17"/>
+      <c r="F33" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="56">
+      <c r="A34" s="34">
         <v>9</v>
       </c>
-      <c r="B34" s="57"/>
+      <c r="B34" s="35"/>
       <c r="C34" s="1"/>
       <c r="D34" s="2"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="22">
+      <c r="E34" s="17"/>
+      <c r="F34" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="56">
+      <c r="A35" s="34">
         <v>10</v>
       </c>
-      <c r="B35" s="57"/>
+      <c r="B35" s="35"/>
       <c r="C35" s="1"/>
       <c r="D35" s="2"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="22">
+      <c r="E35" s="17"/>
+      <c r="F35" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="56">
+      <c r="A36" s="34">
         <v>11</v>
       </c>
-      <c r="B36" s="57"/>
+      <c r="B36" s="35"/>
       <c r="C36" s="1"/>
       <c r="D36" s="2"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="22">
+      <c r="E36" s="17"/>
+      <c r="F36" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="34"/>
-      <c r="B37" s="35"/>
-      <c r="C37" s="35"/>
-      <c r="D37" s="35"/>
-      <c r="E37" s="20" t="s">
+      <c r="A37" s="38"/>
+      <c r="B37" s="39"/>
+      <c r="C37" s="39"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="F37" s="23">
+      <c r="F37" s="22">
         <f>SUM(F26:F36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="39" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="12" t="s">
+      <c r="B39" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="10"/>
-      <c r="B40" s="33"/>
-      <c r="C40" s="33"/>
-      <c r="D40" s="33"/>
-      <c r="E40" s="33"/>
-      <c r="F40" s="33"/>
-    </row>
-    <row r="42" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="10"/>
-      <c r="B42" s="33"/>
-      <c r="C42" s="33"/>
-      <c r="D42" s="33"/>
-      <c r="E42" s="33"/>
-      <c r="F42" s="33"/>
-    </row>
-    <row r="43" spans="1:6" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
+      <c r="A40" s="57" t="s">
+        <v>29</v>
+      </c>
+      <c r="B40" s="57"/>
+      <c r="C40" s="57"/>
+      <c r="D40" s="57"/>
+      <c r="E40" s="57"/>
+      <c r="F40" s="57"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="57"/>
+      <c r="B41" s="57"/>
+      <c r="C41" s="57"/>
+      <c r="D41" s="57"/>
+      <c r="E41" s="57"/>
+      <c r="F41" s="57"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="57"/>
+      <c r="B42" s="57"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="57"/>
+      <c r="E42" s="57"/>
+      <c r="F42" s="57"/>
+    </row>
+    <row r="43" spans="1:6" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="B43" s="54"/>
+      <c r="C43" s="54"/>
+      <c r="D43" s="54"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
     </row>
-    <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:6" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="31"/>
-      <c r="B45" s="31"/>
-      <c r="C45" s="31"/>
-      <c r="D45" s="31"/>
-      <c r="E45" s="31"/>
-      <c r="F45" s="31"/>
+    <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="54"/>
+      <c r="B44" s="54"/>
+      <c r="C44" s="54"/>
+      <c r="D44" s="54"/>
+    </row>
+    <row r="45" spans="1:6" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="36"/>
+      <c r="B45" s="36"/>
+      <c r="C45" s="36"/>
+      <c r="D45" s="36"/>
+      <c r="E45" s="36"/>
+      <c r="F45" s="36"/>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="31"/>
-      <c r="B46" s="31"/>
-      <c r="C46" s="31"/>
-      <c r="D46" s="31"/>
-      <c r="E46" s="31"/>
-      <c r="F46" s="31"/>
+      <c r="A46" s="36"/>
+      <c r="B46" s="36"/>
+      <c r="C46" s="36"/>
+      <c r="D46" s="36"/>
+      <c r="E46" s="36"/>
+      <c r="F46" s="36"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="31"/>
-      <c r="B47" s="31"/>
-      <c r="C47" s="31"/>
-      <c r="D47" s="31"/>
-      <c r="E47" s="31"/>
-      <c r="F47" s="31"/>
+      <c r="A47" s="36"/>
+      <c r="B47" s="36"/>
+      <c r="C47" s="36"/>
+      <c r="D47" s="36"/>
+      <c r="E47" s="36"/>
+      <c r="F47" s="36"/>
     </row>
     <row r="49" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="4" t="s">
@@ -2583,7 +1755,7 @@
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="14" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2593,16 +1765,16 @@
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B52" s="32" t="s">
+      <c r="B52" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="C52" s="32"/>
+      <c r="C52" s="37"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B53" s="32" t="s">
+      <c r="B53" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="C53" s="32"/>
+      <c r="C53" s="37"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55"/>
@@ -3061,27 +2233,26 @@
       <c r="G107"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="19">
+    <mergeCell ref="C1:F8"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="A20:F22"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A15:F17"/>
     <mergeCell ref="A47:F47"/>
     <mergeCell ref="B52:C52"/>
     <mergeCell ref="B53:C53"/>
     <mergeCell ref="A37:D37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B42:F42"/>
     <mergeCell ref="A45:F45"/>
     <mergeCell ref="A46:F46"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="A40:F42"/>
+    <mergeCell ref="A43:D44"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.11811023622047245" footer="0.19685039370078741"/>
@@ -3113,64 +2284,71 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D1"/>
-      <c r="E1"/>
-      <c r="F1"/>
-      <c r="G1"/>
-      <c r="H1"/>
-      <c r="I1"/>
+      <c r="E1" s="59" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
     </row>
     <row r="2" spans="1:10" ht="15.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D2"/>
-      <c r="E2"/>
-      <c r="F2"/>
-      <c r="G2"/>
-      <c r="H2"/>
-      <c r="I2"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D3"/>
-      <c r="E3"/>
-      <c r="F3"/>
-      <c r="G3"/>
-      <c r="H3"/>
-      <c r="I3"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="60"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D4"/>
-      <c r="E4"/>
-      <c r="F4"/>
-      <c r="G4"/>
-      <c r="H4"/>
-      <c r="I4"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D5"/>
-      <c r="E5"/>
-      <c r="F5"/>
-      <c r="G5"/>
-      <c r="H5"/>
-      <c r="I5"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D6"/>
-      <c r="E6"/>
-      <c r="F6"/>
-      <c r="G6"/>
-      <c r="H6"/>
-      <c r="I6"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
     </row>
     <row r="7" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D7"/>
-      <c r="E7"/>
-      <c r="F7"/>
-      <c r="G7"/>
-      <c r="H7"/>
-      <c r="I7"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="60"/>
+      <c r="G7" s="60"/>
+      <c r="H7" s="60"/>
+      <c r="I7" s="60"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
         <v>25</v>
       </c>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
@@ -3197,7 +2375,7 @@
       <c r="I10" s="41"/>
     </row>
     <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
+      <c r="A11" s="12"/>
       <c r="B11" s="40" t="s">
         <v>14</v>
       </c>
@@ -3245,40 +2423,42 @@
       <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:10" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="10"/>
-      <c r="B15" s="33"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="14"/>
-    </row>
-    <row r="16" spans="1:10" s="13" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
+      <c r="A15" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="55"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="55"/>
+      <c r="E15" s="55"/>
+      <c r="F15" s="55"/>
+      <c r="G15" s="55"/>
+      <c r="H15" s="55"/>
+      <c r="I15" s="55"/>
+      <c r="J15" s="13"/>
+    </row>
+    <row r="16" spans="1:10" s="12" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="55"/>
+      <c r="B16" s="55"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="55"/>
+      <c r="E16" s="55"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="55"/>
+      <c r="H16" s="55"/>
+      <c r="I16" s="55"/>
     </row>
     <row r="17" spans="1:9" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="10"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="33"/>
-    </row>
-    <row r="18" spans="1:9" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="55"/>
+      <c r="B17" s="55"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="55"/>
+      <c r="F17" s="55"/>
+      <c r="G17" s="55"/>
+      <c r="H17" s="55"/>
+      <c r="I17" s="55"/>
+    </row>
+    <row r="18" spans="1:9" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -3302,42 +2482,44 @@
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
     </row>
-    <row r="20" spans="1:9" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="10"/>
-      <c r="B20" s="33"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="33"/>
+    <row r="20" spans="1:9" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="61" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="61"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="61"/>
+      <c r="G20" s="61"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="61"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
+      <c r="A21" s="61"/>
+      <c r="B21" s="61"/>
+      <c r="C21" s="61"/>
+      <c r="D21" s="61"/>
+      <c r="E21" s="61"/>
+      <c r="F21" s="61"/>
+      <c r="G21" s="61"/>
+      <c r="H21" s="61"/>
+      <c r="I21" s="61"/>
     </row>
     <row r="22" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="10"/>
-      <c r="B22" s="33"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="33"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="33"/>
-    </row>
-    <row r="23" spans="1:9" s="11" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="61"/>
+      <c r="B22" s="61"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="61"/>
+      <c r="F22" s="61"/>
+      <c r="G22" s="61"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="61"/>
+    </row>
+    <row r="23" spans="1:9" s="10" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
-      <c r="B23" s="27"/>
+      <c r="B23" s="26"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
@@ -3347,416 +2529,419 @@
       <c r="I23" s="3"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="49" t="s">
-        <v>0</v>
-      </c>
-      <c r="B24" s="36" t="s">
+      <c r="A24" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="36" t="s">
+      <c r="C24" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="D24" s="36" t="s">
+      <c r="D24" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="E24" s="36" t="s">
+      <c r="E24" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="F24" s="36" t="s">
+      <c r="F24" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="G24" s="58" t="s">
+      <c r="G24" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="H24" s="59"/>
-      <c r="I24" s="38" t="s">
+      <c r="H24" s="48"/>
+      <c r="I24" s="45" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:9" s="11" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="50"/>
-      <c r="B25" s="37"/>
-      <c r="C25" s="37"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="30" t="s">
+    <row r="25" spans="1:9" s="10" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="53"/>
+      <c r="B25" s="44"/>
+      <c r="C25" s="44"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="H25" s="30" t="s">
+      <c r="H25" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="I25" s="39"/>
-    </row>
-    <row r="26" spans="1:9" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="28">
+      <c r="I25" s="46"/>
+    </row>
+    <row r="26" spans="1:9" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
         <v>1</v>
       </c>
-      <c r="B26" s="29"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="24">
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="23">
         <f>D26*E26</f>
         <v>0</v>
       </c>
-      <c r="G26" s="25">
+      <c r="G26" s="24">
         <v>0.12</v>
       </c>
       <c r="H26" s="2">
         <f>F26*0.12</f>
         <v>0</v>
       </c>
-      <c r="I26" s="24">
+      <c r="I26" s="23">
         <f>F26+H26</f>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="11" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="28">
+    <row r="27" spans="1:9" s="10" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
         <v>2</v>
       </c>
-      <c r="B27" s="29"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="24">
+      <c r="B27" s="28"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="23">
         <f t="shared" ref="F27:F36" si="0">D27*E27</f>
         <v>0</v>
       </c>
-      <c r="G27" s="25">
+      <c r="G27" s="24">
         <v>0.12</v>
       </c>
       <c r="H27" s="2">
         <f t="shared" ref="H27:H36" si="1">F27*0.12</f>
         <v>0</v>
       </c>
-      <c r="I27" s="24">
+      <c r="I27" s="23">
         <f t="shared" ref="I27:I36" si="2">F27+H27</f>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="11" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="28">
+    <row r="28" spans="1:9" s="10" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
         <v>3</v>
       </c>
-      <c r="B28" s="29"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="24">
+      <c r="B28" s="28"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G28" s="25">
+      <c r="G28" s="24">
         <v>0.12</v>
       </c>
       <c r="H28" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I28" s="24">
+      <c r="I28" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="28">
+    <row r="29" spans="1:9" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
         <v>4</v>
       </c>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="24">
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G29" s="25">
+      <c r="G29" s="24">
         <v>0.12</v>
       </c>
       <c r="H29" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I29" s="24">
+      <c r="I29" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="28">
+    <row r="30" spans="1:9" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
         <v>5</v>
       </c>
-      <c r="B30" s="29"/>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="24">
+      <c r="B30" s="28"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="23">
         <f t="shared" ref="F30" si="3">D30*E30</f>
         <v>0</v>
       </c>
-      <c r="G30" s="25">
+      <c r="G30" s="24">
         <v>0.12</v>
       </c>
       <c r="H30" s="2">
         <f t="shared" ref="H30" si="4">F30*0.12</f>
         <v>0</v>
       </c>
-      <c r="I30" s="24">
+      <c r="I30" s="23">
         <f t="shared" ref="I30" si="5">F30+H30</f>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="28">
+    <row r="31" spans="1:9" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
         <v>6</v>
       </c>
-      <c r="B31" s="29"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="24">
+      <c r="B31" s="28"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="23">
         <f t="shared" ref="F31" si="6">D31*E31</f>
         <v>0</v>
       </c>
-      <c r="G31" s="25">
+      <c r="G31" s="24">
         <v>0.12</v>
       </c>
       <c r="H31" s="2">
         <f t="shared" ref="H31" si="7">F31*0.12</f>
         <v>0</v>
       </c>
-      <c r="I31" s="24">
+      <c r="I31" s="23">
         <f t="shared" ref="I31" si="8">F31+H31</f>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="28">
+    <row r="32" spans="1:9" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
         <v>7</v>
       </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="24">
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="23">
         <f t="shared" ref="F32" si="9">D32*E32</f>
         <v>0</v>
       </c>
-      <c r="G32" s="25">
+      <c r="G32" s="24">
         <v>0.12</v>
       </c>
       <c r="H32" s="2">
         <f t="shared" ref="H32" si="10">F32*0.12</f>
         <v>0</v>
       </c>
-      <c r="I32" s="24">
+      <c r="I32" s="23">
         <f t="shared" ref="I32" si="11">F32+H32</f>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="28">
+    <row r="33" spans="1:9" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
         <v>8</v>
       </c>
-      <c r="B33" s="29"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="24">
+      <c r="B33" s="28"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="23">
         <f t="shared" ref="F33" si="12">D33*E33</f>
         <v>0</v>
       </c>
-      <c r="G33" s="25">
+      <c r="G33" s="24">
         <v>0.12</v>
       </c>
       <c r="H33" s="2">
         <f t="shared" ref="H33" si="13">F33*0.12</f>
         <v>0</v>
       </c>
-      <c r="I33" s="24">
+      <c r="I33" s="23">
         <f t="shared" ref="I33" si="14">F33+H33</f>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="28">
+    <row r="34" spans="1:9" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
         <v>9</v>
       </c>
-      <c r="B34" s="29"/>
-      <c r="C34" s="29"/>
-      <c r="D34" s="29"/>
-      <c r="E34" s="29"/>
-      <c r="F34" s="24">
+      <c r="B34" s="28"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="23">
         <f t="shared" ref="F34" si="15">D34*E34</f>
         <v>0</v>
       </c>
-      <c r="G34" s="25">
+      <c r="G34" s="24">
         <v>0.12</v>
       </c>
       <c r="H34" s="2">
         <f t="shared" ref="H34" si="16">F34*0.12</f>
         <v>0</v>
       </c>
-      <c r="I34" s="24">
+      <c r="I34" s="23">
         <f t="shared" ref="I34" si="17">F34+H34</f>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="28">
+    <row r="35" spans="1:9" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
         <v>10</v>
       </c>
-      <c r="B35" s="29"/>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="29"/>
-      <c r="F35" s="24">
+      <c r="B35" s="28"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="23">
         <f t="shared" ref="F35" si="18">D35*E35</f>
         <v>0</v>
       </c>
-      <c r="G35" s="25">
+      <c r="G35" s="24">
         <v>0.12</v>
       </c>
       <c r="H35" s="2">
         <f t="shared" ref="H35" si="19">F35*0.12</f>
         <v>0</v>
       </c>
-      <c r="I35" s="24">
+      <c r="I35" s="23">
         <f t="shared" ref="I35" si="20">F35+H35</f>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="28">
+    <row r="36" spans="1:9" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
         <v>11</v>
       </c>
-      <c r="B36" s="29"/>
-      <c r="C36" s="29"/>
-      <c r="D36" s="29"/>
-      <c r="E36" s="29"/>
-      <c r="F36" s="24">
+      <c r="B36" s="28"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G36" s="25">
+      <c r="G36" s="24">
         <v>0.12</v>
       </c>
       <c r="H36" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I36" s="24">
+      <c r="I36" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="46" t="s">
+      <c r="A37" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="B37" s="47"/>
-      <c r="C37" s="47"/>
-      <c r="D37" s="47"/>
-      <c r="E37" s="47"/>
-      <c r="F37" s="47"/>
-      <c r="G37" s="47"/>
-      <c r="H37" s="48"/>
-      <c r="I37" s="26">
+      <c r="B37" s="50"/>
+      <c r="C37" s="50"/>
+      <c r="D37" s="50"/>
+      <c r="E37" s="50"/>
+      <c r="F37" s="50"/>
+      <c r="G37" s="50"/>
+      <c r="H37" s="51"/>
+      <c r="I37" s="25">
         <f>SUM(I26:I36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="12" t="s">
+      <c r="B39" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="10"/>
-      <c r="B40" s="45"/>
-      <c r="C40" s="45"/>
-      <c r="D40" s="45"/>
-      <c r="E40" s="45"/>
-      <c r="F40" s="45"/>
-      <c r="G40" s="45"/>
-      <c r="H40" s="45"/>
-      <c r="I40" s="45"/>
+      <c r="A40" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="B40" s="55"/>
+      <c r="C40" s="55"/>
+      <c r="D40" s="55"/>
+      <c r="E40" s="55"/>
+      <c r="F40" s="55"/>
+      <c r="G40" s="55"/>
+      <c r="H40" s="55"/>
+      <c r="I40" s="55"/>
     </row>
     <row r="41" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="10"/>
-      <c r="B41" s="15"/>
-      <c r="C41" s="43"/>
-      <c r="D41" s="43"/>
-      <c r="E41" s="44"/>
-      <c r="F41" s="44"/>
-      <c r="G41" s="44"/>
-      <c r="H41" s="44"/>
-      <c r="I41" s="15"/>
+      <c r="A41" s="55"/>
+      <c r="B41" s="55"/>
+      <c r="C41" s="55"/>
+      <c r="D41" s="55"/>
+      <c r="E41" s="55"/>
+      <c r="F41" s="55"/>
+      <c r="G41" s="55"/>
+      <c r="H41" s="55"/>
+      <c r="I41" s="55"/>
     </row>
     <row r="42" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="10"/>
-      <c r="B42" s="10"/>
-      <c r="C42" s="10"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
-      <c r="I42" s="10"/>
-    </row>
-    <row r="43" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="3"/>
-      <c r="B43" s="51" t="s">
+      <c r="A42" s="55"/>
+      <c r="B42" s="55"/>
+      <c r="C42" s="55"/>
+      <c r="D42" s="55"/>
+      <c r="E42" s="55"/>
+      <c r="F42" s="55"/>
+      <c r="G42" s="55"/>
+      <c r="H42" s="55"/>
+      <c r="I42" s="55"/>
+    </row>
+    <row r="43" spans="1:9" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="C43" s="51"/>
-      <c r="D43" s="51"/>
-      <c r="E43" s="51"/>
+      <c r="B43" s="54"/>
+      <c r="C43" s="54"/>
+      <c r="D43" s="54"/>
+      <c r="E43" s="54"/>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
     </row>
     <row r="44" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="51"/>
-      <c r="C44" s="51"/>
-      <c r="D44" s="51"/>
-      <c r="E44" s="51"/>
-    </row>
-    <row r="45" spans="1:9" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="31"/>
-      <c r="B45" s="31"/>
-      <c r="C45" s="31"/>
-      <c r="D45" s="31"/>
-      <c r="E45" s="31"/>
-      <c r="F45" s="31"/>
-      <c r="G45" s="31"/>
-      <c r="H45" s="31"/>
-      <c r="I45" s="31"/>
+      <c r="A44" s="54"/>
+      <c r="B44" s="54"/>
+      <c r="C44" s="54"/>
+      <c r="D44" s="54"/>
+      <c r="E44" s="54"/>
+    </row>
+    <row r="45" spans="1:9" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="36"/>
+      <c r="B45" s="36"/>
+      <c r="C45" s="36"/>
+      <c r="D45" s="36"/>
+      <c r="E45" s="36"/>
+      <c r="F45" s="36"/>
+      <c r="G45" s="36"/>
+      <c r="H45" s="36"/>
+      <c r="I45" s="36"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="31"/>
-      <c r="B46" s="31"/>
-      <c r="C46" s="31"/>
-      <c r="D46" s="31"/>
-      <c r="E46" s="31"/>
-      <c r="F46" s="31"/>
-      <c r="G46" s="31"/>
-      <c r="H46" s="31"/>
-      <c r="I46" s="31"/>
+      <c r="A46" s="36"/>
+      <c r="B46" s="36"/>
+      <c r="C46" s="36"/>
+      <c r="D46" s="36"/>
+      <c r="E46" s="36"/>
+      <c r="F46" s="36"/>
+      <c r="G46" s="36"/>
+      <c r="H46" s="36"/>
+      <c r="I46" s="36"/>
     </row>
     <row r="47" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="31"/>
-      <c r="B47" s="31"/>
-      <c r="C47" s="31"/>
-      <c r="D47" s="31"/>
-      <c r="E47" s="31"/>
-      <c r="F47" s="31"/>
-      <c r="G47" s="31"/>
-      <c r="H47" s="31"/>
-      <c r="I47" s="31"/>
+      <c r="A47" s="36"/>
+      <c r="B47" s="36"/>
+      <c r="C47" s="36"/>
+      <c r="D47" s="36"/>
+      <c r="E47" s="36"/>
+      <c r="F47" s="36"/>
+      <c r="G47" s="36"/>
+      <c r="H47" s="36"/>
+      <c r="I47" s="36"/>
     </row>
     <row r="49" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="4" t="s">
@@ -3764,10 +2949,10 @@
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B50" s="32" t="s">
+      <c r="B50" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="C50" s="32"/>
+      <c r="C50" s="37"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B51" s="4" t="s">
@@ -3775,18 +2960,18 @@
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B52" s="32" t="s">
+      <c r="B52" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="C52" s="32"/>
-      <c r="D52" s="32"/>
+      <c r="C52" s="37"/>
+      <c r="D52" s="37"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B53" s="32" t="s">
+      <c r="B53" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="C53" s="32"/>
-      <c r="D53" s="32"/>
+      <c r="C53" s="37"/>
+      <c r="D53" s="37"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I54" s="3" t="s">
@@ -4400,7 +3585,16 @@
       <c r="J109"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="24">
+    <mergeCell ref="E1:I8"/>
+    <mergeCell ref="A15:I17"/>
+    <mergeCell ref="A20:I22"/>
+    <mergeCell ref="A40:I42"/>
+    <mergeCell ref="A43:E44"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A13:I13"/>
     <mergeCell ref="B52:D52"/>
     <mergeCell ref="B53:D53"/>
     <mergeCell ref="G24:H24"/>
@@ -4416,34 +3610,10 @@
     <mergeCell ref="A45:I45"/>
     <mergeCell ref="A46:I46"/>
     <mergeCell ref="A47:I47"/>
-    <mergeCell ref="B43:E44"/>
-    <mergeCell ref="B17:I17"/>
-    <mergeCell ref="A10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B15:I15"/>
-    <mergeCell ref="B20:I20"/>
-    <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A13:I13"/>
-    <mergeCell ref="B22:I22"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="B40:I40"/>
-    <mergeCell ref="G41:H41"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.11811023622047245" footer="0.19685039370078741"/>
   <pageSetup paperSize="9" scale="82" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96332496-AF1C-46B4-A885-0AC2B5E7F7B1}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.48958333333333331" right="0.375" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
 </file>
--- a/public/templates/kp-template-11.xlsx
+++ b/public/templates/kp-template-11.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mp-calc-2.0\price-calc\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D989325-A430-4600-BAF4-A3154BC6EE0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D3F5CB6-85DB-4055-AEE9-18D508C112EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="23160" windowHeight="11910" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="КП-1 (с НДС) RUS" sheetId="16" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="33">
   <si>
     <t>№</t>
   </si>
@@ -162,6 +162,14 @@
 Тел.: +99871291-37-75.Р/с 2020 8000 3048 2507 1001
 в ОПЕРУ АКБ «ASIA ALLIANCE BANK», МФО 01095
                                        ИНН 301262117 ОКЭД 46730 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">☐ В наличии    ☐ Комплексность    ☐ Временное хранение    ☐ Скидка    ☐ Доставка       
+☐ Шеф. Монтаж    ☐ Эксклюзивность    ☐ Ускоренная поставка    ☐ Доп. скидка    ☐ PMG    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">☐ Фундамент    ☐ Фасад    ☐ СК    ☐ ЛКМ    ☐ Звукоизоляция    ☐ Линейный водоотвод   
+☐ Мансарда    ☐ Терраса    ☐ ПК    ☐ Полы    ☐ Опалубочная система    </t>
   </si>
 </sst>
 </file>
@@ -818,6 +826,36 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -830,26 +868,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -871,30 +903,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1308,57 +1316,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C1" s="58" t="s">
+      <c r="C1" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
     </row>
     <row r="2" spans="1:7" ht="15.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
     </row>
     <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="58"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58"/>
-      <c r="F7" s="58"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="58"/>
-      <c r="D8" s="58"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="58"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
@@ -1369,40 +1377,40 @@
       <c r="F9" s="8"/>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
     </row>
     <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
     </row>
     <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="42"/>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
+      <c r="A12" s="44"/>
+      <c r="B12" s="44"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
     </row>
     <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="42"/>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
+      <c r="A13" s="44"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
     </row>
     <row r="14" spans="1:7" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
@@ -1415,31 +1423,31 @@
       <c r="F14" s="4"/>
     </row>
     <row r="15" spans="1:7" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="55" t="s">
+      <c r="A15" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="55"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="55"/>
+      <c r="B15" s="45"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
       <c r="G15" s="13"/>
     </row>
     <row r="16" spans="1:7" s="12" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="55"/>
-      <c r="B16" s="55"/>
-      <c r="C16" s="55"/>
-      <c r="D16" s="55"/>
-      <c r="E16" s="55"/>
-      <c r="F16" s="55"/>
+      <c r="A16" s="45"/>
+      <c r="B16" s="45"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
     </row>
     <row r="17" spans="1:6" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="55"/>
-      <c r="B17" s="55"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="55"/>
+      <c r="A17" s="45"/>
+      <c r="B17" s="45"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
     </row>
     <row r="18" spans="1:6" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
@@ -1460,30 +1468,30 @@
       <c r="F19" s="4"/>
     </row>
     <row r="20" spans="1:6" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="56" t="s">
+      <c r="A20" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="56"/>
-      <c r="C20" s="56"/>
-      <c r="D20" s="56"/>
-      <c r="E20" s="56"/>
-      <c r="F20" s="56"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="56"/>
-      <c r="B21" s="56"/>
-      <c r="C21" s="56"/>
-      <c r="D21" s="56"/>
-      <c r="E21" s="56"/>
-      <c r="F21" s="56"/>
+      <c r="A21" s="41"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
     </row>
     <row r="22" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="56"/>
-      <c r="B22" s="56"/>
-      <c r="C22" s="56"/>
-      <c r="D22" s="56"/>
-      <c r="E22" s="56"/>
-      <c r="F22" s="56"/>
+      <c r="A22" s="41"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
     </row>
     <row r="23" spans="1:6" s="10" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
@@ -1500,26 +1508,26 @@
       <c r="B24" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="43" t="s">
+      <c r="C24" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="D24" s="43" t="s">
+      <c r="D24" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="E24" s="43" t="s">
+      <c r="E24" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="F24" s="45" t="s">
+      <c r="F24" s="39" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:6" s="10" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="31"/>
       <c r="B25" s="16"/>
-      <c r="C25" s="44"/>
-      <c r="D25" s="44"/>
-      <c r="E25" s="44"/>
-      <c r="F25" s="46"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="40"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="32">
@@ -1665,10 +1673,10 @@
       </c>
     </row>
     <row r="37" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="38"/>
-      <c r="B37" s="39"/>
-      <c r="C37" s="39"/>
-      <c r="D37" s="39"/>
+      <c r="A37" s="48"/>
+      <c r="B37" s="49"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="49"/>
       <c r="E37" s="19" t="s">
         <v>3</v>
       </c>
@@ -1684,70 +1692,70 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="57" t="s">
+      <c r="A40" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="B40" s="57"/>
-      <c r="C40" s="57"/>
-      <c r="D40" s="57"/>
-      <c r="E40" s="57"/>
-      <c r="F40" s="57"/>
+      <c r="B40" s="50"/>
+      <c r="C40" s="50"/>
+      <c r="D40" s="50"/>
+      <c r="E40" s="50"/>
+      <c r="F40" s="50"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="57"/>
-      <c r="B41" s="57"/>
-      <c r="C41" s="57"/>
-      <c r="D41" s="57"/>
-      <c r="E41" s="57"/>
-      <c r="F41" s="57"/>
+      <c r="A41" s="50"/>
+      <c r="B41" s="50"/>
+      <c r="C41" s="50"/>
+      <c r="D41" s="50"/>
+      <c r="E41" s="50"/>
+      <c r="F41" s="50"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="57"/>
-      <c r="B42" s="57"/>
-      <c r="C42" s="57"/>
-      <c r="D42" s="57"/>
-      <c r="E42" s="57"/>
-      <c r="F42" s="57"/>
+      <c r="A42" s="50"/>
+      <c r="B42" s="50"/>
+      <c r="C42" s="50"/>
+      <c r="D42" s="50"/>
+      <c r="E42" s="50"/>
+      <c r="F42" s="50"/>
     </row>
     <row r="43" spans="1:6" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="54" t="s">
+      <c r="A43" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="B43" s="54"/>
-      <c r="C43" s="54"/>
-      <c r="D43" s="54"/>
+      <c r="B43" s="51"/>
+      <c r="C43" s="51"/>
+      <c r="D43" s="51"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
     </row>
     <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="54"/>
-      <c r="B44" s="54"/>
-      <c r="C44" s="54"/>
-      <c r="D44" s="54"/>
+      <c r="A44" s="51"/>
+      <c r="B44" s="51"/>
+      <c r="C44" s="51"/>
+      <c r="D44" s="51"/>
     </row>
     <row r="45" spans="1:6" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="36"/>
-      <c r="B45" s="36"/>
-      <c r="C45" s="36"/>
-      <c r="D45" s="36"/>
-      <c r="E45" s="36"/>
-      <c r="F45" s="36"/>
+      <c r="A45" s="46"/>
+      <c r="B45" s="46"/>
+      <c r="C45" s="46"/>
+      <c r="D45" s="46"/>
+      <c r="E45" s="46"/>
+      <c r="F45" s="46"/>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="36"/>
-      <c r="B46" s="36"/>
-      <c r="C46" s="36"/>
-      <c r="D46" s="36"/>
-      <c r="E46" s="36"/>
-      <c r="F46" s="36"/>
+      <c r="A46" s="46"/>
+      <c r="B46" s="46"/>
+      <c r="C46" s="46"/>
+      <c r="D46" s="46"/>
+      <c r="E46" s="46"/>
+      <c r="F46" s="46"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="36"/>
-      <c r="B47" s="36"/>
-      <c r="C47" s="36"/>
-      <c r="D47" s="36"/>
-      <c r="E47" s="36"/>
-      <c r="F47" s="36"/>
+      <c r="A47" s="46"/>
+      <c r="B47" s="46"/>
+      <c r="C47" s="46"/>
+      <c r="D47" s="46"/>
+      <c r="E47" s="46"/>
+      <c r="F47" s="46"/>
     </row>
     <row r="49" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="4" t="s">
@@ -1765,16 +1773,16 @@
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B52" s="37" t="s">
+      <c r="B52" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="C52" s="37"/>
+      <c r="C52" s="47"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B53" s="37" t="s">
+      <c r="B53" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="C53" s="37"/>
+      <c r="C53" s="47"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55"/>
@@ -2234,6 +2242,14 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A40:F42"/>
+    <mergeCell ref="A43:D44"/>
     <mergeCell ref="C1:F8"/>
     <mergeCell ref="D24:D25"/>
     <mergeCell ref="F24:F25"/>
@@ -2245,14 +2261,6 @@
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A15:F17"/>
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A45:F45"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A40:F42"/>
-    <mergeCell ref="A43:D44"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.11811023622047245" footer="0.19685039370078741"/>
@@ -2284,71 +2292,71 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D1"/>
-      <c r="E1" s="59" t="s">
+      <c r="E1" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
     </row>
     <row r="2" spans="1:10" ht="15.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D2"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D3"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D4"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D5"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D6"/>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
-      <c r="I6" s="60"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
     </row>
     <row r="7" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D7"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="60"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="60"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
-      <c r="H8" s="60"/>
-      <c r="I8" s="60"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="53"/>
+      <c r="G8" s="53"/>
+      <c r="H8" s="53"/>
+      <c r="I8" s="53"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
@@ -2362,52 +2370,52 @@
       <c r="I9" s="8"/>
     </row>
     <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="41"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
     </row>
     <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="40"/>
-      <c r="I11" s="40"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
     </row>
     <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="42"/>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42"/>
+      <c r="A12" s="44"/>
+      <c r="B12" s="44"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="42"/>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="42"/>
+      <c r="A13" s="44"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
     </row>
     <row r="14" spans="1:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
@@ -2423,40 +2431,40 @@
       <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:10" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="55" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="55"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="55"/>
-      <c r="G15" s="55"/>
-      <c r="H15" s="55"/>
-      <c r="I15" s="55"/>
+      <c r="A15" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="45"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="45"/>
       <c r="J15" s="13"/>
     </row>
     <row r="16" spans="1:10" s="12" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="55"/>
-      <c r="B16" s="55"/>
-      <c r="C16" s="55"/>
-      <c r="D16" s="55"/>
-      <c r="E16" s="55"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="55"/>
-      <c r="H16" s="55"/>
-      <c r="I16" s="55"/>
+      <c r="A16" s="45"/>
+      <c r="B16" s="45"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="45"/>
+      <c r="I16" s="45"/>
     </row>
     <row r="17" spans="1:9" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="55"/>
-      <c r="B17" s="55"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="55"/>
-      <c r="G17" s="55"/>
-      <c r="H17" s="55"/>
-      <c r="I17" s="55"/>
+      <c r="A17" s="45"/>
+      <c r="B17" s="45"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="45"/>
+      <c r="H17" s="45"/>
+      <c r="I17" s="45"/>
     </row>
     <row r="18" spans="1:9" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
@@ -2483,39 +2491,39 @@
       <c r="I19" s="4"/>
     </row>
     <row r="20" spans="1:9" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="61" t="s">
+      <c r="A20" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="61"/>
-      <c r="C20" s="61"/>
-      <c r="D20" s="61"/>
-      <c r="E20" s="61"/>
-      <c r="F20" s="61"/>
-      <c r="G20" s="61"/>
-      <c r="H20" s="61"/>
-      <c r="I20" s="61"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="54"/>
+      <c r="I20" s="54"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="61"/>
-      <c r="B21" s="61"/>
-      <c r="C21" s="61"/>
-      <c r="D21" s="61"/>
-      <c r="E21" s="61"/>
-      <c r="F21" s="61"/>
-      <c r="G21" s="61"/>
-      <c r="H21" s="61"/>
-      <c r="I21" s="61"/>
+      <c r="A21" s="54"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="54"/>
+      <c r="H21" s="54"/>
+      <c r="I21" s="54"/>
     </row>
     <row r="22" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="61"/>
-      <c r="B22" s="61"/>
-      <c r="C22" s="61"/>
-      <c r="D22" s="61"/>
-      <c r="E22" s="61"/>
-      <c r="F22" s="61"/>
-      <c r="G22" s="61"/>
-      <c r="H22" s="61"/>
-      <c r="I22" s="61"/>
+      <c r="A22" s="54"/>
+      <c r="B22" s="54"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="54"/>
     </row>
     <row r="23" spans="1:9" s="10" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
@@ -2529,46 +2537,46 @@
       <c r="I23" s="3"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="B24" s="43" t="s">
+      <c r="A24" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="43" t="s">
+      <c r="C24" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="D24" s="43" t="s">
+      <c r="D24" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="E24" s="43" t="s">
+      <c r="E24" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="F24" s="43" t="s">
+      <c r="F24" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="G24" s="47" t="s">
+      <c r="G24" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="H24" s="48"/>
-      <c r="I24" s="45" t="s">
+      <c r="H24" s="56"/>
+      <c r="I24" s="39" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:9" s="10" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="53"/>
-      <c r="B25" s="44"/>
-      <c r="C25" s="44"/>
-      <c r="D25" s="44"/>
-      <c r="E25" s="44"/>
-      <c r="F25" s="44"/>
+      <c r="A25" s="61"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
       <c r="G25" s="29" t="s">
         <v>22</v>
       </c>
       <c r="H25" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="I25" s="46"/>
+      <c r="I25" s="40"/>
     </row>
     <row r="26" spans="1:9" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="27">
@@ -2835,16 +2843,16 @@
       </c>
     </row>
     <row r="37" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="49" t="s">
+      <c r="A37" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="B37" s="50"/>
-      <c r="C37" s="50"/>
-      <c r="D37" s="50"/>
-      <c r="E37" s="50"/>
-      <c r="F37" s="50"/>
-      <c r="G37" s="50"/>
-      <c r="H37" s="51"/>
+      <c r="B37" s="58"/>
+      <c r="C37" s="58"/>
+      <c r="D37" s="58"/>
+      <c r="E37" s="58"/>
+      <c r="F37" s="58"/>
+      <c r="G37" s="58"/>
+      <c r="H37" s="59"/>
       <c r="I37" s="25">
         <f>SUM(I26:I36)</f>
         <v>0</v>
@@ -2856,92 +2864,92 @@
       </c>
     </row>
     <row r="40" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="B40" s="55"/>
-      <c r="C40" s="55"/>
-      <c r="D40" s="55"/>
-      <c r="E40" s="55"/>
-      <c r="F40" s="55"/>
-      <c r="G40" s="55"/>
-      <c r="H40" s="55"/>
-      <c r="I40" s="55"/>
+      <c r="A40" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="B40" s="45"/>
+      <c r="C40" s="45"/>
+      <c r="D40" s="45"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="45"/>
+      <c r="G40" s="45"/>
+      <c r="H40" s="45"/>
+      <c r="I40" s="45"/>
     </row>
     <row r="41" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="55"/>
-      <c r="B41" s="55"/>
-      <c r="C41" s="55"/>
-      <c r="D41" s="55"/>
-      <c r="E41" s="55"/>
-      <c r="F41" s="55"/>
-      <c r="G41" s="55"/>
-      <c r="H41" s="55"/>
-      <c r="I41" s="55"/>
+      <c r="A41" s="45"/>
+      <c r="B41" s="45"/>
+      <c r="C41" s="45"/>
+      <c r="D41" s="45"/>
+      <c r="E41" s="45"/>
+      <c r="F41" s="45"/>
+      <c r="G41" s="45"/>
+      <c r="H41" s="45"/>
+      <c r="I41" s="45"/>
     </row>
     <row r="42" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="55"/>
-      <c r="B42" s="55"/>
-      <c r="C42" s="55"/>
-      <c r="D42" s="55"/>
-      <c r="E42" s="55"/>
-      <c r="F42" s="55"/>
-      <c r="G42" s="55"/>
-      <c r="H42" s="55"/>
-      <c r="I42" s="55"/>
+      <c r="A42" s="45"/>
+      <c r="B42" s="45"/>
+      <c r="C42" s="45"/>
+      <c r="D42" s="45"/>
+      <c r="E42" s="45"/>
+      <c r="F42" s="45"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="45"/>
+      <c r="I42" s="45"/>
     </row>
     <row r="43" spans="1:9" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="54" t="s">
+      <c r="A43" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="B43" s="54"/>
-      <c r="C43" s="54"/>
-      <c r="D43" s="54"/>
-      <c r="E43" s="54"/>
+      <c r="B43" s="51"/>
+      <c r="C43" s="51"/>
+      <c r="D43" s="51"/>
+      <c r="E43" s="51"/>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
     </row>
     <row r="44" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="54"/>
-      <c r="B44" s="54"/>
-      <c r="C44" s="54"/>
-      <c r="D44" s="54"/>
-      <c r="E44" s="54"/>
+      <c r="A44" s="51"/>
+      <c r="B44" s="51"/>
+      <c r="C44" s="51"/>
+      <c r="D44" s="51"/>
+      <c r="E44" s="51"/>
     </row>
     <row r="45" spans="1:9" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="36"/>
-      <c r="B45" s="36"/>
-      <c r="C45" s="36"/>
-      <c r="D45" s="36"/>
-      <c r="E45" s="36"/>
-      <c r="F45" s="36"/>
-      <c r="G45" s="36"/>
-      <c r="H45" s="36"/>
-      <c r="I45" s="36"/>
+      <c r="A45" s="46"/>
+      <c r="B45" s="46"/>
+      <c r="C45" s="46"/>
+      <c r="D45" s="46"/>
+      <c r="E45" s="46"/>
+      <c r="F45" s="46"/>
+      <c r="G45" s="46"/>
+      <c r="H45" s="46"/>
+      <c r="I45" s="46"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="36"/>
-      <c r="B46" s="36"/>
-      <c r="C46" s="36"/>
-      <c r="D46" s="36"/>
-      <c r="E46" s="36"/>
-      <c r="F46" s="36"/>
-      <c r="G46" s="36"/>
-      <c r="H46" s="36"/>
-      <c r="I46" s="36"/>
+      <c r="A46" s="46"/>
+      <c r="B46" s="46"/>
+      <c r="C46" s="46"/>
+      <c r="D46" s="46"/>
+      <c r="E46" s="46"/>
+      <c r="F46" s="46"/>
+      <c r="G46" s="46"/>
+      <c r="H46" s="46"/>
+      <c r="I46" s="46"/>
     </row>
     <row r="47" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="36"/>
-      <c r="B47" s="36"/>
-      <c r="C47" s="36"/>
-      <c r="D47" s="36"/>
-      <c r="E47" s="36"/>
-      <c r="F47" s="36"/>
-      <c r="G47" s="36"/>
-      <c r="H47" s="36"/>
-      <c r="I47" s="36"/>
+      <c r="A47" s="46"/>
+      <c r="B47" s="46"/>
+      <c r="C47" s="46"/>
+      <c r="D47" s="46"/>
+      <c r="E47" s="46"/>
+      <c r="F47" s="46"/>
+      <c r="G47" s="46"/>
+      <c r="H47" s="46"/>
+      <c r="I47" s="46"/>
     </row>
     <row r="49" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="4" t="s">
@@ -2949,10 +2957,10 @@
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B50" s="37" t="s">
+      <c r="B50" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="C50" s="37"/>
+      <c r="C50" s="47"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B51" s="4" t="s">
@@ -2960,18 +2968,18 @@
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B52" s="37" t="s">
+      <c r="B52" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="C52" s="37"/>
-      <c r="D52" s="37"/>
+      <c r="C52" s="47"/>
+      <c r="D52" s="47"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B53" s="37" t="s">
+      <c r="B53" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="C53" s="37"/>
-      <c r="D53" s="37"/>
+      <c r="C53" s="47"/>
+      <c r="D53" s="47"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I54" s="3" t="s">
@@ -3586,15 +3594,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="E1:I8"/>
-    <mergeCell ref="A15:I17"/>
-    <mergeCell ref="A20:I22"/>
-    <mergeCell ref="A40:I42"/>
-    <mergeCell ref="A43:E44"/>
-    <mergeCell ref="A10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A13:I13"/>
     <mergeCell ref="B52:D52"/>
     <mergeCell ref="B53:D53"/>
     <mergeCell ref="G24:H24"/>
@@ -3610,6 +3609,15 @@
     <mergeCell ref="A45:I45"/>
     <mergeCell ref="A46:I46"/>
     <mergeCell ref="A47:I47"/>
+    <mergeCell ref="E1:I8"/>
+    <mergeCell ref="A15:I17"/>
+    <mergeCell ref="A20:I22"/>
+    <mergeCell ref="A40:I42"/>
+    <mergeCell ref="A43:E44"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A13:I13"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.11811023622047245" footer="0.19685039370078741"/>
